--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T26"/>
+  <dimension ref="A1:T24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
     <col width="16.21875" customWidth="1" style="4" min="3" max="3"/>
@@ -853,54 +853,19 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>受击倾斜效果</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>受击倾斜效果</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>CueHitReaction</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>0.25</v>
-      </c>
+      <c r="B7" s="5" t="n"/>
+      <c r="C7" s="5" t="n"/>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" s="5" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>闪避冷却CD显示</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>闪避冷却CD显示</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="5" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>CueDodgeCooldownUI</t>
-        </is>
-      </c>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="n"/>
       <c r="C9" s="5" t="n"/>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -913,12 +878,14 @@
       <c r="F10" s="5" t="n"/>
     </row>
     <row r="11">
+      <c r="B11" s="5" t="n"/>
       <c r="C11" s="5" t="n"/>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>
       <c r="F11" s="5" t="n"/>
     </row>
     <row r="12">
+      <c r="B12" s="5" t="n"/>
       <c r="C12" s="5" t="n"/>
       <c r="D12" s="5" t="n"/>
       <c r="E12" s="5" t="n"/>
@@ -975,30 +942,16 @@
     </row>
     <row r="20">
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="5" t="n"/>
-    </row>
+    </row>
+    <row r="22"/>
     <row r="23">
       <c r="B23" s="5" t="n"/>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="B25" s="5" t="n"/>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="n"/>
+    <row r="24">
+      <c r="B24" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.gameplayCue.xlsx
@@ -853,11 +853,34 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
+      <c r="B7" s="5" t="n">
+        <v>9301</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>AutoChessBattleHit</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>AutoChess headless hit cue</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="5" t="n"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CueLogging</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>AutoChessBattleHit</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="8">
       <c r="C8" s="5" t="n"/>
